--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>UI/UX 기반 애플리케이션 개발 플랫폼 '넥사크로'를 통해 기업 및 금융기관 대상 소프트웨어 플랫폼 사업을 운영하며, 국내 100대 기업 중 91% 포함한 2,…</t>
+          <t>UI/UX 기반 애플리케이션 개발 플랫폼 '넥사크로'를 통해 기업 및 금융기관 대상 소프트웨어 플랫폼 사업을 운영하며, 국내 100대 기업 중 91% 포함한 2,600여 고객사를 보유하고 있음</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>가정용 및 사무용 의자를 생산·판매하는 전문기업으로, 1995년 독일 그랄사로부터 DUOBACK 특허권의 국내 전용실시권을 취득하고 2004년 특허권을 완전 취득…</t>
+          <t>가정용 및 사무용 의자를 생산·판매하는 전문기업으로, 1995년 독일 그랄사로부터 DUOBACK 특허권의 국내 전용실시권을 취득하고 2004년 특허권을 완전 취득하여 한국인 체형에 맞는 인간공학 의자를 설계·생산함</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>자사 브랜드로 국내 대표 셔츠 브랜드 'YEZAC', 남성복 'BON', 여성복 'Carries Note', 'BON:E'를 보유하며 오프라인과 온라인에 영업기반…</t>
+          <t>자사 브랜드로 국내 대표 셔츠 브랜드 'YEZAC', 남성복 'BON', 여성복 'Carries Note', 'BON:E'를 보유하며 오프라인과 온라인에 영업기반을 두고 있음</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>구미본사 및 서울지점을 기반으로 광고제작 및 매체대행서비스를 주요사업으로 영위하며, TV, Radio, 신문, 잡지 등 4대 매체와 뉴미디어, 옥외, 극장 등 다…</t>
+          <t>구미본사 및 서울지점을 기반으로 광고제작 및 매체대행서비스를 주요사업으로 영위하며, TV, Radio, 신문, 잡지 등 4대 매체와 뉴미디어, 옥외, 극장 등 다양한 매체별 광고물을 제작하고 있음</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>계열사로 (주)에이피홀딩스, (주)넷향기, Hyzen Corp, (주)씨티엘바이오테크가 있으며, 2025년 재무구조 개선을 위해 Solco Biomedical 지…</t>
+          <t>계열사로 (주)에이피홀딩스, (주)넷향기, Hyzen Corp, (주)씨티엘바이오테크가 있으며, 2025년 재무구조 개선을 위해 Solco Biomedical 지분을 매각함</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>선박통신, 항해, 방산, 기타장비 등 30여 기종을 다품종 소량생산하여 국내 130여개, 해외 60여 개국 140여개 현지 대리점을 통해 판매 및 A/S 제공하고…</t>
+          <t>선박통신, 항해, 방산, 기타장비 등 30여 기종을 다품종 소량생산하여 국내 130여개, 해외 60여 개국 140여개 현지 대리점을 통해 판매 및 A/S 제공하고 있음</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>스마트시티와 교통체계 관련 AI 영상분석 솔루션을 개발·판매하며, 고해상도 AI 영상분석 기술로 스마트시티, 커넥티드 모빌리티, 예측형 스마트 안전 산업에서 두각…</t>
+          <t>스마트시티와 교통체계 관련 AI 영상분석 솔루션을 개발·판매하며, 고해상도 AI 영상분석 기술로 스마트시티, 커넥티드 모빌리티, 예측형 스마트 안전 산업에서 두각을 나타내고 있음</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>250여 개 K-뷰티 브랜드 상품을 180여 개 국가에 판매하는 온라인 쇼핑몰 졸스를 기반으로 뷰티사업을 영위하며, 영화 제작 및 투자, VFX 시각특수효과 제작…</t>
+          <t>250여 개 K-뷰티 브랜드 상품을 180여 개 국가에 판매하는 온라인 쇼핑몰 졸스를 기반으로 뷰티사업을 영위하며, 영화 제작 및 투자, VFX 시각특수효과 제작, 외식사업 등 다각화된 사업 포트폴리오를 구축중임</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>선박용 크레인, 해양플랜트용 크레인, 데크머시너리, LPG·LNG Tank 등 선박 및 해양플랜트 관련 기자재를 제조·공급하며, 모터, 감속기 등 선박 기자재의 …</t>
+          <t>선박용 크레인, 해양플랜트용 크레인, 데크머시너리, LPG·LNG Tank 등 선박 및 해양플랜트 관련 기자재를 제조·공급하며, 모터, 감속기 등 선박 기자재의 판매 및 수리 사업을 병행하고 있음</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>게놈 기반 헬스케어, 액체생검 플랫폼, 암 진단/모니터링, 다중오믹스 기반 조기진단의 4가지 핵심 사업을 하고 있으며, Geno-Test, CD-Prime 제품을…</t>
+          <t>게놈 기반 헬스케어, 액체생검 플랫폼, 암 진단/모니터링, 다중오믹스 기반 조기진단의 4가지 핵심 사업을 하고 있으며, Geno-Test, CD-Prime 제품을 판매하고 있음</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>주요 제품으로 Touch Controller IC, Haptic Driver IC, SAR Sensor IC, MST IC 등을 개발, 모바일 기기와 노트북에 적…</t>
+          <t>주요 제품으로 Touch Controller IC, Haptic Driver IC, SAR Sensor IC, MST IC 등을 개발, 모바일 기기와 노트북에 적용하고 있음</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>주 생산품은 황동봉이며 철동합금코일, 동SLAB, 석도금제품, 동볼 등을 생산하여 전기·전자, 반도체, 자동차, 건축, 방위산업 등 전 산업분야에 기초소재를 공급…</t>
+          <t>주 생산품은 황동봉이며 철동합금코일, 동SLAB, 석도금제품, 동볼 등을 생산하여 전기·전자, 반도체, 자동차, 건축, 방위산업 등 전 산업분야에 기초소재를 공급하고 있음</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>베트남 ICH CUBE VIETNAM과 인도 CH Component Pvt. Ltd.를 100% 자회사로 보유하고 있으며, 2023년 메인일렉콤 폴리우레탄 사업부…</t>
+          <t>베트남 ICH CUBE VIETNAM과 인도 CH Component Pvt. Ltd.를 100% 자회사로 보유하고 있으며, 2023년 메인일렉콤 폴리우레탄 사업부문 영업양수로 수직계열화 달성함</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>국내 2개 연구소를 운영하며 프린터 핵심 고무 롤러, 블레이드류 및 카트리지를 HP에 납품하고 있으며, LED PKG, LAMP, 헬스케어 제품을 개발하여 국내외…</t>
+          <t>국내 2개 연구소를 운영하며 프린터 핵심 고무 롤러, 블레이드류 및 카트리지를 HP에 납품하고 있으며, LED PKG, LAMP, 헬스케어 제품을 개발하여 국내외 판매에 주력하고 있음</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>AI 플랫폼 사업은 포털 '줌닷컴', 광고 솔루션 '딥다이브애드', 글로벌 콘텐츠 플랫폼 '봉봉', AI 프로필 '미브', 텍스트 미디어 '이글루스' 등으로 구성…</t>
+          <t>AI 플랫폼 사업은 포털 '줌닷컴', 광고 솔루션 '딥다이브애드', 글로벌 콘텐츠 플랫폼 '봉봉', AI 프로필 '미브', 텍스트 미디어 '이글루스' 등으로 구성됨</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>돼지고기 및 가금류를 건조·훈연·염장·조리 등의 방법으로 가공하여 전통식품(전통 살라미, 베이컨, 납육), 간편식품(간편 소시지), 냉동식품을 생산·판매하는 육가…</t>
+          <t>돼지고기 및 가금류를 건조·훈연·염장·조리 등의 방법으로 가공하여 전통식품(전통 살라미, 베이컨, 납육), 간편식품(간편 소시지), 냉동식품을 생산·판매하는 육가공 업체임</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>동사는 프리미엄 유아동 슈즈 셀렉숍 개념을 도입해 약 30여 개 프리미엄 키즈 브랜드를 독점 및 홀세일 계약으로 판매하며, 기획·디자인·생산·유통을 아우르는 To…</t>
+          <t>동사는 프리미엄 유아동 슈즈 셀렉숍 개념을 도입해 약 30여 개 프리미엄 키즈 브랜드를 독점 및 홀세일 계약으로 판매하며, 기획·디자인·생산·유통을 아우르는 Total Value Chain을 구축함</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>종속회사로 신기술사업금융회사 큐캐피탈파트너스, 북미 패션유통 큐로베스티스, 이스즈 상용차 판매 큐로모터스, 중국 유통법인 지엔코국제무역(닝보)유한공사를 보유하고 …</t>
+          <t>종속회사로 신기술사업금융회사 큐캐피탈파트너스, 북미 패션유통 큐로베스티스, 이스즈 상용차 판매 큐로모터스, 중국 유통법인 지엔코국제무역(닝보)유한공사를 보유하고 있음</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>광고주와 플랫폼, 이용자 모두에게 혜택을 제공하는 모바일 포인트 플랫폼 사업을 영위하고 있으며, B2B 사업인 '애디슨 오퍼월'과 B2C 서비스인 캐시슬라이드, …</t>
+          <t>광고주와 플랫폼, 이용자 모두에게 혜택을 제공하는 모바일 포인트 플랫폼 사업을 영위하고 있으며, B2B 사업인 '애디슨 오퍼월'과 B2C 서비스인 캐시슬라이드, 캐시피드, 칩스 등 앱테크 플랫폼으로 구성됨</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>백화점, 패션 아울렛, 이커머스, 도매, 홈쇼핑 등 다각화된 유통망을 구축하고 있으며, 이탈리아 브랜드 아드노, 컬트, 페슈라와 미국 브랜드 노티카의 국내 독점 …</t>
+          <t>백화점, 패션 아울렛, 이커머스, 도매, 홈쇼핑 등 다각화된 유통망을 구축하고 있으며, 이탈리아 브랜드 아드노, 컬트, 페슈라와 미국 브랜드 노티카의 국내 독점 라이선스를 보유하고 있음</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>국내 최초로 증강현실 엔진과 저작도구를 개발했고, 물리엔진 기반 XR 미들웨어 솔루션 통해 교육, 관광, 의료, 제조, 엔터테인먼트 분야의 XR 서비스 제공하고 …</t>
+          <t>국내 최초로 증강현실 엔진과 저작도구를 개발했고, 물리엔진 기반 XR 미들웨어 솔루션 통해 교육, 관광, 의료, 제조, 엔터테인먼트 분야의 XR 서비스 제공하고 있음</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>IT 인프라 사업부는 서버와 스토리지를 포함한 IT 인프라 구축, 유지보수, 플렉서블 OLED용 신소재, 2차 전지 배터리와 식료품 제조 공장용 산업 X-Ray …</t>
+          <t>IT 인프라 사업부는 서버와 스토리지를 포함한 IT 인프라 구축, 유지보수, 플렉서블 OLED용 신소재, 2차 전지 배터리와 식료품 제조 공장용 산업 X-Ray 검사장비 사업으로 구성됨</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>DVR 등 영상보안장비 및 솔루션 개발/제조를 주요 사업으로 영위하며, 대규모 통합관제솔루션, GIS MAP 시스템, 스마트폴리스 등 다양한 제품군을 출시하고 있…</t>
+          <t>DVR 등 영상보안장비 및 솔루션 개발/제조를 주요 사업으로 영위하며, 대규모 통합관제솔루션, GIS MAP 시스템, 스마트폴리스 등 다양한 제품군을 출시하고 있음</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>중국, 베트남 생산법인을 통해 스마트폰, 전자담배, 미용기기용 코인타입 진동모터와 자동차용 전동모터를 제조하며, 주요 고객은 국내 최대 스마트폰 제조사 및 글로벌…</t>
+          <t>중국, 베트남 생산법인을 통해 스마트폰, 전자담배, 미용기기용 코인타입 진동모터와 자동차용 전동모터를 제조하며, 주요 고객은 국내 최대 스마트폰 제조사 및 글로벌 전자담배 업체임</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>종속회사로 영상처리 하드웨어 전문 실로닉스, 중국 화장품 유통 및 제조사 NEXTEYE technology와 Shanghai Bel-Cosmetic, 반도체검사장…</t>
+          <t>종속회사로 영상처리 하드웨어 전문 실로닉스, 중국 화장품 유통 및 제조사 NEXTEYE technology와 Shanghai Bel-Cosmetic, 반도체검사장비 마인즈아이 등 9개 보유함</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2024년 항공기 시뮬레이터 전문기업 쓰리디아이를 편입하고, 2025년 글로벌 프리미엄 브랜드 호카(HOKA)의 국내 오프라인 리테일 사업부를 인수하여 포트폴리오…</t>
+          <t>2024년 항공기 시뮬레이터 전문기업 쓰리디아이를 편입하고, 2025년 글로벌 프리미엄 브랜드 호카(HOKA)의 국내 오프라인 리테일 사업부를 인수하여 포트폴리오를 다각화하였음</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>선박엔진부품 사업에서 엔진볼트 등 다양한 부품을 제조 판매하고, 산업부품 사업에서는 해양 및 대형 건설·플랜트용 볼트류와 단조품 사업에서는 선박부품을 제조 판매하…</t>
+          <t>선박엔진부품 사업에서 엔진볼트 등 다양한 부품을 제조 판매하고, 산업부품 사업에서는 해양 및 대형 건설·플랜트용 볼트류와 단조품 사업에서는 선박부품을 제조 판매하고 있음</t>
         </is>
       </c>
       <c r="F130" s="4" t="n">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>2019년 컨텐츠 제품 제조 및 판매를 주된 사업으로 영위하는 ㈜위드모바일을 합병하였고, 2022년 이차전지용 리튬 소재 제조 및 판매 사업목적을 추가하여 202…</t>
+          <t>2019년 컨텐츠 제품 제조 및 판매를 주된 사업으로 영위하는 ㈜위드모바일을 합병하였고, 2022년 이차전지용 리튬 소재 제조 및 판매 사업목적을 추가하여 2023년 사명을 리튬포어스로 변경함</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>체외진단 의료기기 전문회사로서 분자진단, 면역진단, 생화학진단 사업을 복합적으로 영위하며, 주요 제품은 분자진단기기(PCR), 면역진단기기, 생화학진단기기와 진단…</t>
+          <t>체외진단 의료기기 전문회사로서 분자진단, 면역진단, 생화학진단 사업을 복합적으로 영위하며, 주요 제품은 분자진단기기(PCR), 면역진단기기, 생화학진단기기와 진단시약 등이 있음</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>바이오유통사업에서는 Thermo Fisher Scientific, MERCK 등과 대리점 계약을 체결해 연구용 시약·기기를 납품하고, ICT사업에서는 영상보안장비…</t>
+          <t>바이오유통사업에서는 Thermo Fisher Scientific, MERCK 등과 대리점 계약을 체결해 연구용 시약·기기를 납품하고, ICT사업에서는 영상보안장비 및 IoT기반 솔루션을 제공하고 있음</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>네트워크, 운영·관리 솔루션 및 정보보안 서비스 제공하는 통합 보안 전문기업으로, 차세대 방화벽, 통합 관제 시스템, 무선 침입 방지 시스템 등 네트워크·보안 솔…</t>
+          <t>네트워크, 운영·관리 솔루션 및 정보보안 서비스 제공하는 통합 보안 전문기업으로, 차세대 방화벽, 통합 관제 시스템, 무선 침입 방지 시스템 등 네트워크·보안 솔루션 구축을 주요 사업으로 하고 있음</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>광고용 사인소재 분야에서 FLEX 원단과 Banner 원단을 제조·판매하며, 전 세계 100여 개국에 고객을 확보한 수출기업으로 국내 시장 점유율 약 60% 이상…</t>
+          <t>광고용 사인소재 분야에서 FLEX 원단과 Banner 원단을 제조·판매하며, 전 세계 100여 개국에 고객을 확보한 수출기업으로 국내 시장 점유율 약 60% 이상을 차지하고 있음</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>자동차 산업의 비포마켓과 애프터마켓을 연결하는 통합형 플랫폼 전략을 바탕으로 'A2B 제품/서비스', '이커머스', 'SPACE ZONE' 세 가지 플랫폼을 중심…</t>
+          <t>자동차 산업의 비포마켓과 애프터마켓을 연결하는 통합형 플랫폼 전략을 바탕으로 'A2B 제품/서비스', '이커머스', 'SPACE ZONE' 세 가지 플랫폼을 중심으로 사업 운영 중임</t>
         </is>
       </c>
       <c r="F156" s="4" t="n">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>동사는 IT 인프라 취약점 진단 자동화, 취약점 관리, 웹쉘 탐지, 웹 취약점 진단, 소스코드 취약점 진단 등 IT 인프라 보안 영역을 아우르는 보안 솔루션 포트…</t>
+          <t>동사는 IT 인프라 취약점 진단 자동화, 취약점 관리, 웹쉘 탐지, 웹 취약점 진단, 소스코드 취약점 진단 등 IT 인프라 보안 영역을 아우르는 보안 솔루션 포트폴리오를 구축하고 있음</t>
         </is>
       </c>
       <c r="F159" s="4" t="n">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>주방용품 중 압력솥 생산·판매 및 OEM에 의한 냄비, 프라이팬류, 전기용품을 취급하고 있으며, 알루미늄·스테인리스 기류 제조, 전기용품 제조, 부동산 임대업 등…</t>
+          <t>주방용품 중 압력솥 생산·판매 및 OEM에 의한 냄비, 프라이팬류, 전기용품을 취급하고 있으며, 알루미늄·스테인리스 기류 제조, 전기용품 제조, 부동산 임대업 등을 영위하고 있음</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>화장품 기획부터 생산까지 제공하는 'TOTAL ONE-STOP Solution Provider'로서 NEOGEN DERMALOGY 등 자체 브랜드와 ODM 사업을…</t>
+          <t>화장품 기획부터 생산까지 제공하는 'TOTAL ONE-STOP Solution Provider'로서 NEOGEN DERMALOGY 등 자체 브랜드와 ODM 사업을 영위하고 있음</t>
         </is>
       </c>
       <c r="F163" s="4" t="n">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>금융권 IT Compliance, AI, Big Data, Cloud 기반으로 ABC산업으로 사업을 확장하고, 클라우드 기반 디지털 플랫폼을 다양한 분야에 제공하…</t>
+          <t>금융권 IT Compliance, AI, Big Data, Cloud 기반으로 ABC산업으로 사업을 확장하고, 클라우드 기반 디지털 플랫폼을 다양한 분야에 제공하고 있음</t>
         </is>
       </c>
       <c r="F168" s="4" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>2019년 미국 Abpro Holdings, Inc.와 이중항체 바이오 의약품 아시아 지역 개발 계약을 체결하고, 2023년 ㈜에이엔에이치를 자회사로 편입하여 반…</t>
+          <t>2019년 미국 Abpro Holdings, Inc.와 이중항체 바이오 의약품 아시아 지역 개발 계약을 체결하고, 2023년 ㈜에이엔에이치를 자회사로 편입하여 반도체 장비 사업에 진출함</t>
         </is>
       </c>
       <c r="F170" s="4" t="n">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>동사는 헤어*바디케어 및 염모제 전문 연구*제조*유통 노하우를 바탕으로 모레모(moremo), 리체나(RICHENNA) 등 다양한 연령의 소비자를 위한 전문적인 …</t>
+          <t>동사는 헤어*바디케어 및 염모제 전문 연구*제조*유통 노하우를 바탕으로 모레모(moremo), 리체나(RICHENNA) 등 다양한 연령의 소비자를 위한 전문적인 브랜드를 운영하고 있음</t>
         </is>
       </c>
       <c r="F183" s="4" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>별도 제조시설 없이 협력업체를 통해 제품을 생산하며, 삼익가구, 스칸디아, 스튜디오슬립 등 자체 브랜드를 보유하고 30여 곳의 온라인 플랫폼을 통해 가성비·가심비…</t>
+          <t>별도 제조시설 없이 협력업체를 통해 제품을 생산하며, 삼익가구, 스칸디아, 스튜디오슬립 등 자체 브랜드를 보유하고 30여 곳의 온라인 플랫폼을 통해 가성비·가심비 제품을 판매하고 있음</t>
         </is>
       </c>
       <c r="F191" s="4" t="n">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>주력 제품인 아연화는 타이어, 고무제품, 페라이트 산업의 핵심 원재료로, 고무공업, 도료, 세라믹, 요업, 사료, 화장품 등 다양한 산업의 기초원료로 활용되고 있…</t>
+          <t>주력 제품인 아연화는 타이어, 고무제품, 페라이트 산업의 핵심 원재료로, 고무공업, 도료, 세라믹, 요업, 사료, 화장품 등 다양한 산업의 기초원료로 활용되고 있음</t>
         </is>
       </c>
       <c r="F215" s="4" t="n">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>OLED, 폴더블, 마이크로LED 등 디스플레이 패널 제조에 필요한 합착기, 탈포기 등을 국내외 기업에 공급하며, 세계 최초 매엽식 탈포기, 곡면 진공합착기를 개…</t>
+          <t>OLED, 폴더블, 마이크로LED 등 디스플레이 패널 제조에 필요한 합착기, 탈포기 등을 국내외 기업에 공급하며, 세계 최초 매엽식 탈포기, 곡면 진공합착기를 개발하여 기술력을 인정받았음</t>
         </is>
       </c>
       <c r="F228" s="4" t="n">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>사업부문은 플랜트, 필터프레스, 건축부문으로 구성되며, 소각·발전설비, 슬러지 재활용, 대기오염방지, 폐수처리, 이차전지 공정설비와 산업용 여과기 제조, '인스빌…</t>
+          <t>사업부문은 플랜트, 필터프레스, 건축부문으로 구성되며, 소각·발전설비, 슬러지 재활용, 대기오염방지, 폐수처리, 이차전지 공정설비와 산업용 여과기 제조, '인스빌' 브랜드 주택개발사업을 영위함</t>
         </is>
       </c>
       <c r="F239" s="4" t="n">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>스낵류, 액상차, 음료 제조해 코스트코, GS리테일 등 대형 B2C 유통회사에 공급하고, 부산·경남 지역에 3개 자체 공장을 보유하며 ODM 및 OEM 서비스를 …</t>
+          <t>스낵류, 액상차, 음료 제조해 코스트코, GS리테일 등 대형 B2C 유통회사에 공급하고, 부산·경남 지역에 3개 자체 공장을 보유하며 ODM 및 OEM 서비스를 제공함</t>
         </is>
       </c>
       <c r="F244" s="4" t="n">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>가전, 사무기기, 자동차, 통신 분야의 STEPPING MOTOR 제조 및 판매하고 있으며, 자동차 공력제어용 ACTUATOR는 내연기관 및 친환경 차량에 장착되…</t>
+          <t>가전, 사무기기, 자동차, 통신 분야의 STEPPING MOTOR 제조 및 판매하고 있으며, 자동차 공력제어용 ACTUATOR는 내연기관 및 친환경 차량에 장착되어 안정적 판매 유지함</t>
         </is>
       </c>
       <c r="F257" s="4" t="n">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>지배회사 (주)카스는 중국, 터키, 독일, 미국 등 5개 종속회사를 보유하고 있으며, 중국 법인은 전자저울 제조·판매, 터키·독일 법인은 판매, 미국 법인은 부동…</t>
+          <t>지배회사 (주)카스는 중국, 터키, 독일, 미국 등 5개 종속회사를 보유하고 있으며, 중국 법인은 전자저울 제조·판매, 터키·독일 법인은 판매, 미국 법인은 부동산 임대업을 하고 있음</t>
         </is>
       </c>
       <c r="F259" s="4" t="n">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>유기합성, 대량생산, 신규결정화 기술로 원료의약품(API), 핵심출발소재(KSM), 중간소재(PI)를 개발하고, 심혈관계 질환 치료제, 만성기관지염치료제 원료를 …</t>
+          <t>유기합성, 대량생산, 신규결정화 기술로 원료의약품(API), 핵심출발소재(KSM), 중간소재(PI)를 개발하고, 심혈관계 질환 치료제, 만성기관지염치료제 원료를 생산·판매함</t>
         </is>
       </c>
       <c r="F262" s="4" t="n">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>주력사업은 전파음영지역에서 기지국 신호를 증폭하여 커버리지 공백 없이 재방사하는 통신중계기 분야로, 국내는 KT를 주요 고객으로 하고 해외는 미국 V사 등과 매출…</t>
+          <t>주력사업은 전파음영지역에서 기지국 신호를 증폭하여 커버리지 공백 없이 재방사하는 통신중계기 분야로, 국내는 KT를 주요 고객으로 하고 해외는 미국 V사 등과 매출 확대 추진 중임</t>
         </is>
       </c>
       <c r="F265" s="4" t="n">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>2016년 일본 대형 손해보험회사 '손보재팬'의 디지털 전환 프로젝트를 수주하여 차세대 시스템 구축을 완료하였으며, 2018년 일본 대기업과 전략적 투자 계약을 …</t>
+          <t>2016년 일본 대형 손해보험회사 '손보재팬'의 디지털 전환 프로젝트를 수주하여 차세대 시스템 구축을 완료하였으며, 2018년 일본 대기업과 전략적 투자 계약을 체결함</t>
         </is>
       </c>
       <c r="F273" s="4" t="n">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>종속회사 클라쎄오토는 폭스바겐코리아 공식 딜러사로 전국 판매 서비스 네트워크를 운영하며, 주요 계열사는 투자, 부동산 개발, 자동차 대여 사업을 통해 포트폴리오를…</t>
+          <t>종속회사 클라쎄오토는 폭스바겐코리아 공식 딜러사로 전국 판매 서비스 네트워크를 운영하며, 주요 계열사는 투자, 부동산 개발, 자동차 대여 사업을 통해 포트폴리오를 확장하고 있음</t>
         </is>
       </c>
       <c r="F274" s="4" t="n">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>사업부문은 LOC, PCB 검사장비 및 자동차용, 전지용 검사장비를 생산하는 장비사업부, 메모리 칩 핵심부품을 임가공하는 부품사업부, 메모리 칩 핵심부품 및 스마…</t>
+          <t>사업부문은 LOC, PCB 검사장비 및 자동차용, 전지용 검사장비를 생산하는 장비사업부, 메모리 칩 핵심부품을 임가공하는 부품사업부, 메모리 칩 핵심부품 및 스마트폰용 PCB를 생산하는 PCB사업부로 구성되어 있음</t>
         </is>
       </c>
       <c r="F280" s="4" t="n">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>크리에이터 중심으로 드라마·영화 등 영상 콘텐츠를 기획·제작하여 방송사, OTT 등에 공급하는 콘텐츠 제작 사업과 아티스트 매니지먼트 사업을 영위하며, 콘텐츠 I…</t>
+          <t>크리에이터 중심으로 드라마·영화 등 영상 콘텐츠를 기획·제작하여 방송사, OTT 등에 공급하는 콘텐츠 제작 사업과 아티스트 매니지먼트 사업을 영위하며, 콘텐츠 IP를 활용한 판권 사업도 전개하고 있음</t>
         </is>
       </c>
       <c r="F283" s="4" t="n">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>광고주와 매체를 연결하는 5개의 모바일 광고 플랫폼을 보유하고 있으며, SSP, DSP, AD Network 등 광고 프로세스 전체를 아우르는 풀스택 플랫폼사로 …</t>
+          <t>광고주와 매체를 연결하는 5개의 모바일 광고 플랫폼을 보유하고 있으며, SSP, DSP, AD Network 등 광고 프로세스 전체를 아우르는 풀스택 플랫폼사로 성장하고 있음</t>
         </is>
       </c>
       <c r="F289" s="4" t="n">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>엔터사업부문에서는 연예인 매니지먼트와 유튜브 콘텐츠 제작을 수행하며, 국내 최고의 연기자, 예능인, 전문가 등 총 60여명과 전속계약을 맺고 다양한 영상 콘텐츠에…</t>
+          <t>엔터사업부문에서는 연예인 매니지먼트와 유튜브 콘텐츠 제작을 수행하며, 국내 최고의 연기자, 예능인, 전문가 등 총 60여명과 전속계약을 맺고 다양한 영상 콘텐츠에 출연하고 있음</t>
         </is>
       </c>
       <c r="F290" s="4" t="n">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Seagate, Intel, GIGABYTE 등 핵심 부품 총판권을 보유하고, 2024년 Sennheiser, 2025년 Dreame 등 프리미엄 브랜드 유통권을…</t>
+          <t>Seagate, Intel, GIGABYTE 등 핵심 부품 총판권을 보유하고, 2024년 Sennheiser, 2025년 Dreame 등 프리미엄 브랜드 유통권을 확보 중임</t>
         </is>
       </c>
       <c r="F291" s="4" t="n">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>동사는 정밀의료 사업과 그린바이오 사업을 영위하고 있으며, 정밀의료 사업에서는 인체 유래 시료로부터 핵산(RNA/DNA)을 추출하는 핵산추출시약과 자동화핵산추출기…</t>
+          <t>동사는 정밀의료 사업과 그린바이오 사업을 영위하고 있으며, 정밀의료 사업에서는 인체 유래 시료로부터 핵산(RNA/DNA)을 추출하는 핵산추출시약과 자동화핵산추출기기를 주력 제품으로 판매하고 있음</t>
         </is>
       </c>
       <c r="F293" s="4" t="n">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>국내외 270여 제조사의 제품을 글로벌 소싱하여 약 3만 가지 실험기기를 유통하는 국내 최대 실험기기 종합 서비스 기업이며, 프리미엄 장비를 전 세계 70여 개국…</t>
+          <t>국내외 270여 제조사의 제품을 글로벌 소싱하여 약 3만 가지 실험기기를 유통하는 국내 최대 실험기기 종합 서비스 기업이며, 프리미엄 장비를 전 세계 70여 개국에 수출하는 글로벌 기업임</t>
         </is>
       </c>
       <c r="F311" s="4" t="n">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>주요 사업으로 화장품사업을 영위하며, 중국시장에 K-뷰티 제품인 'RUE KWAVE'를 런칭하여 한류를 선호하는 중국, 동남아시아, 중동지역의 여성고객을 겨냥하고…</t>
+          <t>주요 사업으로 화장품사업을 영위하며, 중국시장에 K-뷰티 제품인 'RUE KWAVE'를 런칭하여 한류를 선호하는 중국, 동남아시아, 중동지역의 여성고객을 겨냥하고 있음</t>
         </is>
       </c>
       <c r="F314" s="4" t="n">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>주력 사업은 디스플레이 소재와 바이오·제약 소재로 구성되며, 디스플레이 분야에서는 OLED 소재 완제품 및 중간체 합성, 소재 재생(Recycle) 사업을 전개하…</t>
+          <t>주력 사업은 디스플레이 소재와 바이오·제약 소재로 구성되며, 디스플레이 분야에서는 OLED 소재 완제품 및 중간체 합성, 소재 재생(Recycle) 사업을 전개하고 있음</t>
         </is>
       </c>
       <c r="F315" s="4" t="n">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>브라질 법인 SDB, 미국 법인 Saedong America를 보유하고 있으며, 금속압출물, 가변압출물, 사출물 등 자동차용 외장부품을 현대차, 기아 등에 공급하…</t>
+          <t>브라질 법인 SDB, 미국 법인 Saedong America를 보유하고 있으며, 금속압출물, 가변압출물, 사출물 등 자동차용 외장부품을 현대차, 기아 등에 공급하고 있음</t>
         </is>
       </c>
       <c r="F319" s="4" t="n">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>유아동 패션 부문에서 '앤디애플', '젤리스푼', '밀크마일' 등 다수 브랜드를 운영하며, 2021년 영유아 오가닉 스킨케어 브랜드 '오가본' 런칭으로 화장품 사…</t>
+          <t>유아동 패션 부문에서 '앤디애플', '젤리스푼', '밀크마일' 등 다수 브랜드를 운영하며, 2021년 영유아 오가닉 스킨케어 브랜드 '오가본' 런칭으로 화장품 사업으로 영역을 확장하고 있음</t>
         </is>
       </c>
       <c r="F323" s="4" t="n">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>진공성형 기술을 이용한 식품 포장용 플라스틱 용기와 친환경 생분해 원료를 이용한 생분해 필름의 제조·판매를 주력으로 하며, 진공성형, 친환경, 로보틱스 3개 사업…</t>
+          <t>진공성형 기술을 이용한 식품 포장용 플라스틱 용기와 친환경 생분해 원료를 이용한 생분해 필름의 제조·판매를 주력으로 하며, 진공성형, 친환경, 로보틱스 3개 사업부문을 운영하고 있음</t>
         </is>
       </c>
       <c r="F330" s="4" t="n">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>동사는 C-Tag, Encleap, TriO, RFMP 등 자체 개발 원천기술로 분자진단제와 의료용 진단 시약을 개발·판매하며, 백신과 면역항암 치료제를 개발하고…</t>
+          <t>동사는 C-Tag, Encleap, TriO, RFMP 등 자체 개발 원천기술로 분자진단제와 의료용 진단 시약을 개발·판매하며, 백신과 면역항암 치료제를 개발하고 있음</t>
         </is>
       </c>
       <c r="F335" s="4" t="n">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>AI 및 IT 인프라 역량을 보유한 피앤티링크, AI 영상 R&amp;D 전문기업 디블라트 등 주요 자회사와 해외 지분투자·중국 법인을 통해 제작·기술·인프라·글로벌 네…</t>
+          <t>AI 및 IT 인프라 역량을 보유한 피앤티링크, AI 영상 R&amp;D 전문기업 디블라트 등 주요 자회사와 해외 지분투자·중국 법인을 통해 제작·기술·인프라·글로벌 네트워크를 확장 중임</t>
         </is>
       </c>
       <c r="F338" s="4" t="n">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>신속 PCR 기술 기반 현장 분자진단 플랫폼을 상용화하여 분자진단 시스템, 바이오칩, 검사키트 등을 개발·제조하며, 주요 제품을 유럽, 아시아 등 해외에 납품하고…</t>
+          <t>신속 PCR 기술 기반 현장 분자진단 플랫폼을 상용화하여 분자진단 시스템, 바이오칩, 검사키트 등을 개발·제조하며, 주요 제품을 유럽, 아시아 등 해외에 납품하고 있음</t>
         </is>
       </c>
       <c r="F339" s="4" t="n">
@@ -23538,7 +23538,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>극세사 클리너, 나노섬유, 슈퍼섬유, 친환경 섬유 등 섬유산업 전반에 걸쳐 사업을 영위하며, 종속회사 웰크론한텍을 통해 건설·플랜트, 신재생에너지, 폐기물 재활용…</t>
+          <t>극세사 클리너, 나노섬유, 슈퍼섬유, 친환경 섬유 등 섬유산업 전반에 걸쳐 사업을 영위하며, 종속회사 웰크론한텍을 통해 건설·플랜트, 신재생에너지, 폐기물 재활용 등으로 사업영역을 확장하고 있음</t>
         </is>
       </c>
       <c r="F341" s="4" t="n">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>동사는 건강기능식품 제조, 유통 및 판매를 주력 사업으로 영위하며, B2C 전자상거래 플랫폼과 다양한 유통 플랫폼을 통해 건강기능식품과 건강지향식품을 개발·제조하…</t>
+          <t>동사는 건강기능식품 제조, 유통 및 판매를 주력 사업으로 영위하며, B2C 전자상거래 플랫폼과 다양한 유통 플랫폼을 통해 건강기능식품과 건강지향식품을 개발·제조하고 있음</t>
         </is>
       </c>
       <c r="F343" s="4" t="n">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>IoT 기반 데이터 수집 기술과 산업용 AI를 접목한 산업용 AX 플랫폼 'NUBISON AX'를 운영하며, 제조, 공공, 헬스케어 등 다양한 분야의 AI 전환을…</t>
+          <t>IoT 기반 데이터 수집 기술과 산업용 AI를 접목한 산업용 AX 플랫폼 'NUBISON AX'를 운영하며, 제조, 공공, 헬스케어 등 다양한 분야의 AI 전환을 지원하고 있음</t>
         </is>
       </c>
       <c r="F346" s="4" t="n">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>국내 최초 전자서명인증기반 보안운영체제 'Secuve TOS'를 개발하고, 'iGRIFFIN', 'LogGRIFFIN'을 통해 서버보안, 통합계정권한관리, 빅데이…</t>
+          <t>국내 최초 전자서명인증기반 보안운영체제 'Secuve TOS'를 개발하고, 'iGRIFFIN', 'LogGRIFFIN'을 통해 서버보안, 통합계정권한관리, 빅데이터 분석과 통합로그관리를 아우르는 토탈솔루션을 확보함</t>
         </is>
       </c>
       <c r="F348" s="4" t="n">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>주요 종속회사로 온라인 쇼핑몰 '더에르고' 운영사 에르모어, 가이아코퍼레이션, 옥토아이앤씨, 소브 등이 있으며, 당기 중 베스트유통을 편입하여 G7커피 등 유통사…</t>
+          <t>주요 종속회사로 온라인 쇼핑몰 '더에르고' 운영사 에르모어, 가이아코퍼레이션, 옥토아이앤씨, 소브 등이 있으며, 당기 중 베스트유통을 편입하여 G7커피 등 유통사업으로 사업영역을 확장함</t>
         </is>
       </c>
       <c r="F350" s="4" t="n">
@@ -24328,7 +24328,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>장비제조부에서는 stacker system을 제조하며, 진공펌프에 유틸리티 제공, 공정배관 길이 조정, 펌프 소음 억제, 진동 보호 기능 등을 통해 진공 펌프 가…</t>
+          <t>장비제조부에서는 stacker system을 제조하며, 진공펌프에 유틸리티 제공, 공정배관 길이 조정, 펌프 소음 억제, 진동 보호 기능 등을 통해 진공 펌프 가동환경 최적화와 반도체 생산공정 효율에 기여하고 있음</t>
         </is>
       </c>
       <c r="F353" s="4" t="n">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>태양전지 모듈 제조 및 태양광 발전 시스템 설치, 발전사업을 주요사업으로 영위하며, 발전소 유지보수(O&amp;M) 사업과 자회사 에스프리즘을 통한 수소연료전지사업도 수…</t>
+          <t>태양전지 모듈 제조 및 태양광 발전 시스템 설치, 발전사업을 주요사업으로 영위하며, 발전소 유지보수(O&amp;M) 사업과 자회사 에스프리즘을 통한 수소연료전지사업도 수행하고 있음</t>
         </is>
       </c>
       <c r="F354" s="4" t="n">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>주요 사업으로 소형, EV용, ESS용 중대형 2차전지 분리막 연신설비, 코팅기, 추출기, 건조기 장비와 LCD, OLED용 편광필름 제조설비 및 압력용기 장비를…</t>
+          <t>주요 사업으로 소형, EV용, ESS용 중대형 2차전지 분리막 연신설비, 코팅기, 추출기, 건조기 장비와 LCD, OLED용 편광필름 제조설비 및 압력용기 장비를 제작하고 있음</t>
         </is>
       </c>
       <c r="F356" s="4" t="n">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>응급실 및 중환자실에서 필수적으로 사용되는 인공호흡기, 호흡치료기, 환자감시장치를 설계·제조·판매하는 의료기기 전문 제조업체로, 수입제품에 의존하던 인공호흡기를 …</t>
+          <t>응급실 및 중환자실에서 필수적으로 사용되는 인공호흡기, 호흡치료기, 환자감시장치를 설계·제조·판매하는 의료기기 전문 제조업체로, 수입제품에 의존하던 인공호흡기를 국내 최초로 개발하여 상용화에 성공함</t>
         </is>
       </c>
       <c r="F359" s="4" t="n">
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>LCD, OLED, LED 등 디스플레이 패널 제작 FPD Bonding과 Inspection 시스템을 개발·생산하고, 물류자동화 시스템과 화장품 유통 사업을 영…</t>
+          <t>LCD, OLED, LED 등 디스플레이 패널 제작 FPD Bonding과 Inspection 시스템을 개발·생산하고, 물류자동화 시스템과 화장품 유통 사업을 영위함</t>
         </is>
       </c>
       <c r="F360" s="4" t="n">
